--- a/ESTA_バリデーション実装チェックシート.xlsx
+++ b/ESTA_バリデーション実装チェックシート.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,13 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001A3A5C"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +63,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEEFF"/>
+        <bgColor rgb="00DDEEFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -89,6 +124,19 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -455,7 +503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6509,6 +6557,1284 @@
         </is>
       </c>
       <c r="H157" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr"/>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>フェーズ2〜5</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>カメラ機能・自動入力拡張（新規追加）</t>
+        </is>
+      </c>
+      <c r="D159" s="4" t="inlineStr"/>
+      <c r="E159" s="4" t="inlineStr"/>
+      <c r="F159" s="4" t="inlineStr"/>
+      <c r="G159" s="4" t="inlineStr"/>
+      <c r="H159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C160" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="inlineStr">
+        <is>
+          <t>カメラモーダル表示</t>
+        </is>
+      </c>
+      <c r="E160" s="5" t="inlineStr">
+        <is>
+          <t>「📷 カメラで撮影」タップでカメラモーダルが全画面表示される</t>
+        </is>
+      </c>
+      <c r="F160" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G160" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C161" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="inlineStr">
+        <is>
+          <t>人型シルエット描画</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="inlineStr">
+        <is>
+          <t>Canvas に頭部正円＋肩ラインのシルエットが描画される（ellipse禁止・scale禁止）</t>
+        </is>
+      </c>
+      <c r="F161" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G161" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C162" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="inlineStr">
+        <is>
+          <t>リアルタイム明るさ判定</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr">
+        <is>
+          <t>平均輝度70未満で「明るい場所で撮影してください」が表示される</t>
+        </is>
+      </c>
+      <c r="F162" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G162" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C163" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="inlineStr">
+        <is>
+          <t>FaceDetector顔位置判定</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="inlineStr">
+        <is>
+          <t>FaceDetector対応時：顔の中央ズレ&gt;20%で警告メッセージ表示</t>
+        </is>
+      </c>
+      <c r="F163" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G163" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C164" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="inlineStr">
+        <is>
+          <t>FaceDetectorサイズ判定</t>
+        </is>
+      </c>
+      <c r="E164" s="5" t="inlineStr">
+        <is>
+          <t>顔高さ/画像高さ&lt;0.4で「近づいてください」、&gt;0.75で「離れてください」</t>
+        </is>
+      </c>
+      <c r="F164" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G164" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C165" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="inlineStr">
+        <is>
+          <t>自動シャッタートグル</t>
+        </is>
+      </c>
+      <c r="E165" s="5" t="inlineStr">
+        <is>
+          <t>「🔴 自動 OFF」ボタンをタップで「🟢 自動 ON」に切り替わる</t>
+        </is>
+      </c>
+      <c r="F165" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G165" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C166" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="inlineStr">
+        <is>
+          <t>自動シャッター発火</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="inlineStr">
+        <is>
+          <t>ON時：全条件OK 0.5秒継続→「自動撮影します！」ポップアップ→撮影</t>
+        </is>
+      </c>
+      <c r="F166" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G166" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="inlineStr">
+        <is>
+          <t>FaceDetector非対応フォールバック</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>非対応ブラウザでは明るさのみで自動シャッター判定</t>
+        </is>
+      </c>
+      <c r="F167" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G167" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>顔写真カメラガイド</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="inlineStr">
+        <is>
+          <t>EXIF回転補正</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>iOS等のEXIF orientationを読み取り、Canvas描画時に自動回転補正</t>
+        </is>
+      </c>
+      <c r="F168" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G168" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C169" s="5" t="inlineStr">
+        <is>
+          <t>撮影後品質チェック</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="inlineStr">
+        <is>
+          <t>品質スコア表示</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="inlineStr">
+        <is>
+          <t>撮影後に明るさ・解像度・形式の品質チェック結果が表示される</t>
+        </is>
+      </c>
+      <c r="F169" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G169" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B170" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C170" s="5" t="inlineStr">
+        <is>
+          <t>撮影後品質チェック</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="inlineStr">
+        <is>
+          <t>写真使用ボタン</t>
+        </is>
+      </c>
+      <c r="E170" s="5" t="inlineStr">
+        <is>
+          <t>NGがない場合のみ「この写真を使用する」ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="F170" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G170" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B171" s="5" t="inlineStr">
+        <is>
+          <t>フェーズ2</t>
+        </is>
+      </c>
+      <c r="C171" s="5" t="inlineStr">
+        <is>
+          <t>撮影後品質チェック</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="inlineStr">
+        <is>
+          <t>再撮影ボタン</t>
+        </is>
+      </c>
+      <c r="E171" s="5" t="inlineStr">
+        <is>
+          <t>「再撮影する」で再度カメラガイドに戻れる</t>
+        </is>
+      </c>
+      <c r="F171" s="5" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G171" s="5" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>QRボタン表示</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>PC表示時のみ顔写真欄に「📱 スマホから送信（QR）」ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>PeerJS接続・QR生成</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>ボタン押下でPeerID生成→QRコード（qrserver.com）表示</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>5分タイムアウト</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>5分経過でQRがグレーアウトし「期限切れ」メッセージが表示される</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G174" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>SP専用UI表示</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>?peer=XXX URLアクセス時にフォームが非表示→専用UI表示</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>SP撮影→PC転送</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>SP側で撮影→600×600処理→ArrayBufferでPC側へWebRTC送信</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G176" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B177" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D177" s="6" t="inlineStr">
+        <is>
+          <t>PC側プレビュー表示</t>
+        </is>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>受信後PCのモーダルに写真がプレビュー表示され自動でクローズ</t>
+        </is>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G177" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>PeerID1回限り</t>
+        </is>
+      </c>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
+          <t>写真受信後にpeer.destroy()でセッションを破棄</t>
+        </is>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B179" s="6" t="inlineStr">
+        <is>
+          <t>フェーズ3</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>QR+WebRTC転送</t>
+        </is>
+      </c>
+      <c r="D179" s="6" t="inlineStr">
+        <is>
+          <t>フォールバック</t>
+        </is>
+      </c>
+      <c r="E179" s="6" t="inlineStr">
+        <is>
+          <t>getUserMedia失敗時は自動でネイティブカメラ入力に切替</t>
+        </is>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G179" s="6" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="n">
+        <v>21</v>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>撮影品質担保</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>自動背景補正</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
+          <t>撮影後に顔領域外のピクセルを白方向35%ブレンド＋影リフト処理</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="B181" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C181" s="7" t="inlineStr">
+        <is>
+          <t>撮影品質担保</t>
+        </is>
+      </c>
+      <c r="D181" s="7" t="inlineStr">
+        <is>
+          <t>顔コーナーガイド</t>
+        </is>
+      </c>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
+          <t>FaceDetector検出時に顔領域にコーナーブラケット白枠を表示</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="B182" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C182" s="7" t="inlineStr">
+        <is>
+          <t>撮影品質担保</t>
+        </is>
+      </c>
+      <c r="D182" s="7" t="inlineStr">
+        <is>
+          <t>品質スコア0-100</t>
+        </is>
+      </c>
+      <c r="E182" s="7" t="inlineStr">
+        <is>
+          <t>明るさ・顔サイズ・顔位置・背景均一性の4項目でスコアを算出</t>
+        </is>
+      </c>
+      <c r="F182" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G182" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B183" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C183" s="7" t="inlineStr">
+        <is>
+          <t>撮影品質担保</t>
+        </is>
+      </c>
+      <c r="D183" s="7" t="inlineStr">
+        <is>
+          <t>スコア判定ライン</t>
+        </is>
+      </c>
+      <c r="E183" s="7" t="inlineStr">
+        <is>
+          <t>90点以上:✅高品質 / 60-89点:⚠️使用可 / 60未満:❌再撮影推奨</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B184" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C184" s="7" t="inlineStr">
+        <is>
+          <t>撮影品質担保</t>
+        </is>
+      </c>
+      <c r="D184" s="7" t="inlineStr">
+        <is>
+          <t>60未満で使用ボタン非表示</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>スコア60未満の場合「この写真を使用する」ボタンが非表示になる</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="B185" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C185" s="7" t="inlineStr">
+        <is>
+          <t>分析ログ</t>
+        </is>
+      </c>
+      <c r="D185" s="7" t="inlineStr">
+        <is>
+          <t>撮影イベント記録</t>
+        </is>
+      </c>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
+          <t>camera_open/capture/photo_accepted/photo_retakenをlocalStorageに記録</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="B186" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ4</t>
+        </is>
+      </c>
+      <c r="C186" s="7" t="inlineStr">
+        <is>
+          <t>分析ログ</t>
+        </is>
+      </c>
+      <c r="D186" s="7" t="inlineStr">
+        <is>
+          <t>デバッグパネル</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>?debug=1アクセスで起動回数・採用率・平均スコアのパネルが表示される</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C187" s="8" t="inlineStr">
+        <is>
+          <t>パスポートOCR</t>
+        </is>
+      </c>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>OCR自動起動</t>
+        </is>
+      </c>
+      <c r="E187" s="8" t="inlineStr">
+        <is>
+          <t>パスポート画像アップロード完了後に自動でTesseract.js MRZ解析が起動</t>
+        </is>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B188" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C188" s="8" t="inlineStr">
+        <is>
+          <t>パスポートOCR</t>
+        </is>
+      </c>
+      <c r="D188" s="8" t="inlineStr">
+        <is>
+          <t>MRZ解析・自動入力</t>
+        </is>
+      </c>
+      <c r="E188" s="8" t="inlineStr">
+        <is>
+          <t>MRZ読取後に姓・名・パスポート番号・生年月日・有効期限・性別を自動入力</t>
+        </is>
+      </c>
+      <c r="F188" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C189" s="8" t="inlineStr">
+        <is>
+          <t>パスポートOCR</t>
+        </is>
+      </c>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>読取状況表示</t>
+        </is>
+      </c>
+      <c r="E189" s="8" t="inlineStr">
+        <is>
+          <t>「🔍 読み取り中」→「✅ X項目自動入力」または「❌ 読取失敗」を表示</t>
+        </is>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B190" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C190" s="8" t="inlineStr">
+        <is>
+          <t>パスポートOCR</t>
+        </is>
+      </c>
+      <c r="D190" s="8" t="inlineStr">
+        <is>
+          <t>再読み取りボタン</t>
+        </is>
+      </c>
+      <c r="E190" s="8" t="inlineStr">
+        <is>
+          <t>完了後に「🔄 再読み取り」ボタンが表示され手動で再実行できる</t>
+        </is>
+      </c>
+      <c r="F190" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C191" s="8" t="inlineStr">
+        <is>
+          <t>autofill最適化</t>
+        </is>
+      </c>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>autocomplete属性</t>
+        </is>
+      </c>
+      <c r="E191" s="8" t="inlineStr">
+        <is>
+          <t>surname/givenName/email/phoneNumber/street/zipCodeにautocomplete属性を付与</t>
+        </is>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B192" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C192" s="8" t="inlineStr">
+        <is>
+          <t>入力履歴保存</t>
+        </is>
+      </c>
+      <c r="D192" s="8" t="inlineStr">
+        <is>
+          <t>ステップ移動時に自動保存</t>
+        </is>
+      </c>
+      <c r="E192" s="8" t="inlineStr">
+        <is>
+          <t>nextStep()実行時にフォームデータをlocalStorageに自動保存</t>
+        </is>
+      </c>
+      <c r="F192" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G192" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C193" s="8" t="inlineStr">
+        <is>
+          <t>入力履歴保存</t>
+        </is>
+      </c>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>復元バー表示</t>
+        </is>
+      </c>
+      <c r="E193" s="8" t="inlineStr">
+        <is>
+          <t>次回アクセス時に「📋 前回の入力内容があります」バーが10秒表示される</t>
+        </is>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B194" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C194" s="8" t="inlineStr">
+        <is>
+          <t>入力履歴保存</t>
+        </is>
+      </c>
+      <c r="D194" s="8" t="inlineStr">
+        <is>
+          <t>7日自動削除</t>
+        </is>
+      </c>
+      <c r="E194" s="8" t="inlineStr">
+        <is>
+          <t>保存から7日以上経過したドラフトは自動削除される</t>
+        </is>
+      </c>
+      <c r="F194" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G194" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>フェーズ5</t>
+        </is>
+      </c>
+      <c r="C195" s="8" t="inlineStr">
+        <is>
+          <t>メールサジェスト</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>ドメイン候補表示</t>
+        </is>
+      </c>
+      <c r="E195" s="8" t="inlineStr">
+        <is>
+          <t>@入力後にgmail.com/yahoo.co.jp等のドメイン候補が最大4件表示される</t>
+        </is>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>2026/04/06</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H157"/>
